--- a/Bills_generated.xlsx
+++ b/Bills_generated.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Bills" sheetId="1" state="visible" r:id="rId1"/>
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.42578125" customWidth="1" min="11" max="11"/>
@@ -486,19 +486,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Imperial Blue</t>
+          <t>GRAND MASTER CRANBERRY VODKA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>750 ml</t>
+          <t>180</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -507,17 +507,22 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>9360</v>
+        <v>14160</v>
       </c>
       <c r="I2" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>10725</v>
+        <v>151230</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
         </is>
       </c>
     </row>
@@ -527,16 +532,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MCD No 1</t>
+          <t>MAGIC MOMENTS GRAIN VODKA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>750 ml</t>
+          <t>750</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>600</v>
+        <v>1120</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
@@ -545,20 +550,25 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>2320</v>
+        <v>3300</v>
       </c>
       <c r="I3" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10725</v>
+        <v>151230</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
         </is>
       </c>
     </row>
@@ -568,38 +578,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MCD No 1</t>
+          <t>MAGIC MOMENTS GRAIN VODKA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>375 ml</t>
+          <t>375</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>300</v>
+        <v>560</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>6900</v>
+        <v>3300</v>
       </c>
       <c r="I4" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>10725</v>
+        <v>151230</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
         </is>
       </c>
     </row>
@@ -609,217 +624,222 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MCD No 1</t>
+          <t>MAGIC MOMENTS JAMUN SPICY MINT VODKA (PET)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>180 ml</t>
+          <t>180</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="E5" t="n">
         <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>145</v>
+        <v>25440</v>
       </c>
       <c r="I5" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10725</v>
+        <v>151230</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Imperial Blue</t>
+          <t>MAGIC MOMENTS JAMUN VODKA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>750 ml</t>
+          <t>750</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>800</v>
+        <v>1120</v>
       </c>
       <c r="E6" t="n">
         <v>20</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
-        <v>28080</v>
+        <v>3300</v>
       </c>
       <c r="I6" t="n">
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>960</v>
+        <v>151230</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>New Party</t>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>04-04-2026</t>
+          <t>04-05-2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MCD No 1</t>
+          <t>MAGIC MOMENTS JAMUN VODKA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>750 ml</t>
+          <t>375</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>6960</v>
+        <v>3300</v>
       </c>
       <c r="I7" t="n">
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>960</v>
+        <v>151230</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>New Party</t>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>04-04-2026</t>
+          <t>04-05-2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MCD No 1</t>
+          <t>MAGIC MOMENTS JAMUN VODKA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>180 ml</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H8" t="n">
-        <v>13920</v>
+        <v>6840</v>
       </c>
       <c r="I8" t="n">
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>960</v>
+        <v>151230</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>New Party</t>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>04-04-2026</t>
+          <t>04-05-2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Imperial Blue</t>
+          <t>ROYAL STAG WHY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>750 ml</t>
+          <t>750</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>800</v>
+        <v>1070</v>
       </c>
       <c r="E9" t="n">
         <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>9360</v>
+        <v>7350</v>
       </c>
       <c r="I9" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-755</v>
+        <v>151230</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>New Vendor</t>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -830,42 +850,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Imperial Blue</t>
+          <t>ROYAL STAG WHY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>375 ml</t>
+          <t>375</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>520</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>17550</v>
+        <v>12240</v>
       </c>
       <c r="I10" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-755</v>
+        <v>151230</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>New Vendor</t>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -876,42 +896,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Imperial Blue</t>
+          <t>ROYAL STAG WHY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>180 ml</t>
+          <t>180</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E11" t="n">
         <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>10335</v>
+        <v>58800</v>
       </c>
       <c r="I11" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-755</v>
+        <v>151230</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>New Vendor</t>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -922,42 +942,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Imperial Blue</t>
+          <t>ROYAL STAG WHY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>750 ml</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>800</v>
+        <v>140</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>18720</v>
+        <v>13200</v>
       </c>
       <c r="I12" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-290</v>
+        <v>151230</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Wow Party</t>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -968,42 +988,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Imperial Blue</t>
+          <t>AFTER DARK BLUE WHISKY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>375 ml</t>
+          <t>180</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>400</v>
+        <v>220</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1170</v>
+        <v>10320</v>
       </c>
       <c r="I13" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-290</v>
+        <v>167550</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Wow Party</t>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1014,42 +1034,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Imperial Blue</t>
+          <t>GRAND MASTER CRANBERRY VODKA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>90 ml</t>
+          <t>180</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>28080</v>
+        <v>14160</v>
       </c>
       <c r="I14" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-290</v>
+        <v>167550</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Wow Party</t>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1060,20 +1080,20 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MCD No 1</t>
+          <t>MAGIC MOMENTS GRAIN VODKA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>750 ml</t>
+          <t>750</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>600</v>
+        <v>1120</v>
       </c>
       <c r="E15" t="n">
         <v>20</v>
@@ -1085,20 +1105,2550 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>1740</v>
+        <v>3300</v>
       </c>
       <c r="I15" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-290</v>
+        <v>167550</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Wow Party</t>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS GRAIN VODKA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>560</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>167550</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN SPICY MINT VODKA (PET)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>270</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>25440</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>167550</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN VODKA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>167550</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN VODKA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>560</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>167550</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN VODKA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>145</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>48</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6840</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>167550</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RADICO NV GOA GIN MML</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>130</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>167550</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1070</v>
+      </c>
+      <c r="E22" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7350</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>167550</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>520</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12240</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>167550</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>250</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>58800</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>167550</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>140</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>13200</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>167550</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AFTER DARK BLUE WHISKY</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>220</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>10320</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GRAND MASTER CRANBERRY VODKA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>300</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>14160</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS GRAIN VODKA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS GRAIN VODKA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>560</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS GRAIN VODKA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>145</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>24</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3420</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN SPICY MINT VODKA (PET)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>270</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>25440</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN VODKA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E32" t="n">
+        <v>20</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN VODKA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>560</v>
+      </c>
+      <c r="E33" t="n">
+        <v>10</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN VODKA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>145</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>48</v>
+      </c>
+      <c r="H34" t="n">
+        <v>6840</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MCD NO.1 RESERVE WHY. PET</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>210</v>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>19680</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>RADICO NV GOA GIN MML</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>130</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1070</v>
+      </c>
+      <c r="E37" t="n">
+        <v>20</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>7</v>
+      </c>
+      <c r="H37" t="n">
+        <v>7350</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>520</v>
+      </c>
+      <c r="E38" t="n">
+        <v>10</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>12240</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>3</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>250</v>
+      </c>
+      <c r="E39" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>58800</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>3</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>90(100)</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>140</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>13750</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AFTER DARK BLUE WHISKY</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>220</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>10320</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GRAND MASTER CRANBERRY VODKA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>300</v>
+      </c>
+      <c r="E42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>14160</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS GRAIN VODKA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E43" t="n">
+        <v>20</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS GRAIN VODKA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>560</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS GRAIN VODKA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>145</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>24</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3420</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN SPICY MINT VODKA (PET)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>270</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>25440</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN VODKA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E47" t="n">
+        <v>20</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN VODKA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>560</v>
+      </c>
+      <c r="E48" t="n">
+        <v>10</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN VODKA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>145</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>48</v>
+      </c>
+      <c r="H49" t="n">
+        <v>6840</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MCD NO.1 RESERVE WHY. PET</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>210</v>
+      </c>
+      <c r="E50" t="n">
+        <v>5</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>19680</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>RADICO NV GOA GIN MML</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>130</v>
+      </c>
+      <c r="E51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>4</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1070</v>
+      </c>
+      <c r="E52" t="n">
+        <v>20</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>7</v>
+      </c>
+      <c r="H52" t="n">
+        <v>7350</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>520</v>
+      </c>
+      <c r="E53" t="n">
+        <v>10</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>12240</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>250</v>
+      </c>
+      <c r="E54" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>58800</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>90(100)</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>140</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>13750</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AFTER DARK BLUE WHISKY</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>220</v>
+      </c>
+      <c r="E56" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>10320</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GRAND MASTER CRANBERRY VODKA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>300</v>
+      </c>
+      <c r="E57" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>14160</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS GRAIN VODKA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E58" t="n">
+        <v>20</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS GRAIN VODKA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>560</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>6</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS GRAIN VODKA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>145</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>24</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3420</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>4</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN SPICY MINT VODKA (PET)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>270</v>
+      </c>
+      <c r="E61" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>25440</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN VODKA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E62" t="n">
+        <v>20</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>3</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN VODKA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>560</v>
+      </c>
+      <c r="E63" t="n">
+        <v>10</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MAGIC MOMENTS JAMUN VODKA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>145</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>48</v>
+      </c>
+      <c r="H64" t="n">
+        <v>6840</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MCD NO.1 RESERVE WHY. PET</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>210</v>
+      </c>
+      <c r="E65" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>19680</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>4</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>RADICO NV GOA GIN MML</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>130</v>
+      </c>
+      <c r="E66" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>4</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1070</v>
+      </c>
+      <c r="E67" t="n">
+        <v>20</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>7</v>
+      </c>
+      <c r="H67" t="n">
+        <v>7350</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>520</v>
+      </c>
+      <c r="E68" t="n">
+        <v>10</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>12240</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>250</v>
+      </c>
+      <c r="E69" t="n">
+        <v>5</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>58800</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>04-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>4</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ROYAL STAG WHY</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>90(100)</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>140</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>13750</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>191200</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Rahul Jadhav Sir Shivur Bangla</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t>04-05-2026</t>
         </is>
